--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -511,271 +511,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
-    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24866EC1-C4D7-40DE-B828-356DD24E0004}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4105C94B-9105-48E8-95C3-F904ED30622E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E42ED8E-6F91-4BA1-8E4C-F1BEDBB968FD}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -511,4 +511,271 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
+    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE832452-F964-4BB1-BA25-7FE2C6DA9032}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E233F154-9711-49F1-8843-AF32312BE4AF}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8F59110-0A4D-470C-BD9F-9305112CBD17}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -434,75 +434,1230 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3918786000010015036</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>3918786000010071142</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>25-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3918786000010015036</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3918786000010071140</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3918786000010015036</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3918786000010071138</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3918786000010015036</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>3918786000010071136</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3918786000010015036</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>3918786000010071134</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3918786000010015036</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MURROMONE</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>3918786000010071132</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3918786000010015034</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3918786000010071130</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3918786000010015034</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>3918786000010071128</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3918786000010015034</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3918786000010071126</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>OFENSIVA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3918786000010015038</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>OFENSIVA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>3918786000010071124</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>OFENSIVA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3918786000010015038</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>OFENSIVA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>3918786000010071122</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>OFENSIVA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3918786000010015038</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>OFENSIVA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>3918786000010071120</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3918786000010015034</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3918786000010071118</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3918786000010015034</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3918786000010071116</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3918786000010015034</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>3918786000010071114</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>10-Mar-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Marlene João Alfredo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>3918786000006032043</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Marlene João Alfredo</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>NAMARIESSA</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>3918786000010015004</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>NAMARIESSA</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Sessão_1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>3918786000010015294</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Ribaue</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -511,271 +1666,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
-    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE832452-F964-4BB1-BA25-7FE2C6DA9032}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E233F154-9711-49F1-8843-AF32312BE4AF}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8F59110-0A4D-470C-BD9F-9305112CBD17}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -434,27 +434,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3918786000006032015</t>
+          <t>3918786000006032027</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -464,22 +464,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3918786000010015036</t>
+          <t>3918786000010015014</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -489,17 +489,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>3918786000010071142</t>
+          <t>3918786000010125016</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -511,27 +511,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25-Apr-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3918786000006032015</t>
+          <t>3918786000006032027</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -541,22 +541,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3918786000010015036</t>
+          <t>3918786000010015014</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -566,49 +566,49 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3918786000010071140</t>
+          <t>3918786000010125014</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>18-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3918786000006032015</t>
+          <t>3918786000006032027</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -618,22 +618,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3918786000010015036</t>
+          <t>3918786000010015014</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -643,17 +643,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3918786000010071138</t>
+          <t>3918786000010125012</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -665,27 +665,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>18-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3918786000006032015</t>
+          <t>3918786000006032027</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -695,42 +695,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3918786000010015036</t>
+          <t>3918786000010015014</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>26</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3918786000010071136</t>
+          <t>3918786000010125010</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -742,22 +742,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3918786000006032015</t>
+          <t>3918786000006032027</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -772,22 +772,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3918786000010015036</t>
+          <t>3918786000010015014</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -797,17 +797,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>26</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3918786000010071134</t>
+          <t>3918786000010125008</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -819,72 +819,72 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18-Apr-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3918786000006032015</t>
+          <t>3918786000006032027</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3918786000010015036</t>
+          <t>3918786000010015014</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3918786000010071132</t>
+          <t>3918786000010125006</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -896,27 +896,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18-Apr-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3918786000006032015</t>
+          <t>3918786000006032027</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -926,22 +926,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>JARDIM</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3918786000010015034</t>
+          <t>3918786000010015014</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>JARDIM</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3918786000010071130</t>
+          <t>3918786000010125004</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -973,27 +973,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18-Apr-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3918786000006032015</t>
+          <t>3918786000006032027</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>JARDIM</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3918786000010015034</t>
+          <t>3918786000010015014</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>JARDIM</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3918786000010071128</t>
+          <t>3918786000010125002</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1080,22 +1080,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>JARDIM</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3918786000010015034</t>
+          <t>3918786000010015036</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>JARDIM</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3918786000010071126</t>
+          <t>3918786000010071142</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1127,7 +1127,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18-Apr-2026</t>
+          <t>25-Apr-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1157,37 +1157,37 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3918786000010015038</t>
+          <t>3918786000010015036</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3918786000010071124</t>
+          <t>3918786000010071140</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1234,22 +1234,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3918786000010015038</t>
+          <t>3918786000010015036</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3918786000010071122</t>
+          <t>3918786000010071138</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1311,37 +1311,37 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3918786000010015038</t>
+          <t>3918786000010015036</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3918786000010071120</t>
+          <t>3918786000010071136</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1388,37 +1388,37 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>JARDIM</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3918786000010015034</t>
+          <t>3918786000010015036</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>JARDIM</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>3918786000010071118</t>
+          <t>3918786000010071134</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1455,37 +1455,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>JARDIM</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3918786000010015034</t>
+          <t>3918786000010015036</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>JARDIM</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3918786000010071116</t>
+          <t>3918786000010071132</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1557,22 +1557,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3918786000010071114</t>
+          <t>3918786000010071130</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1589,75 +1589,691 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3918786000010015034</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>3918786000010071128</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3918786000010015034</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>3918786000010071126</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>OFENSIVA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>3918786000010015038</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>OFENSIVA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>3918786000010071124</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>OFENSIVA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3918786000010015038</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>OFENSIVA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>3918786000010071122</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>OFENSIVA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3918786000010015038</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>OFENSIVA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>3918786000010071120</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>3918786000010015034</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>3918786000010071118</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3918786000010015034</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>3918786000010071116</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3918786000010015034</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>3918786000010071114</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>10-Mar-2026</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Marlene João Alfredo</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>3918786000006032043</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Marlene João Alfredo</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>NAMARIESSA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>3918786000010015004</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>NAMARIESSA</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Sessão_1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>3918786000010015294</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Ribaue</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1666,4 +2282,271 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
+    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F32588A0-EB87-4A3C-B29A-8EC6DF0F2EEB}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E53F34B-A4DC-4293-A35A-78FDC71CDCCE}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{254E9B65-A011-43F5-807A-8FAA662601D3}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -2282,271 +2282,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
-    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F32588A0-EB87-4A3C-B29A-8EC6DF0F2EEB}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E53F34B-A4DC-4293-A35A-78FDC71CDCCE}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{254E9B65-A011-43F5-807A-8FAA662601D3}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -2282,4 +2282,271 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
+    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56F87ECE-8656-400B-8D83-D753050D3958}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4C137D1-4261-4C63-90BE-E1CA65744A05}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{096B70F7-A02A-493C-8415-4ACDDDD1EFEB}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -17401,13 +17401,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{886B57F4-FB93-4460-8987-489E8BD28674}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9995DF3C-924C-46F5-BC3E-CAE32DE0E3A1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B835883-E63B-4F00-869A-DF1F31E8E508}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EDA3F80-EF27-48B7-A482-B455D7906537}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DCA8372-0F13-4469-8764-9082DE0A94F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38C66B80-772C-472F-A618-CD2A183EF0AB}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O218"/>
+  <dimension ref="A1:O219"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -434,27 +434,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Marlene João Alfredo</t>
+          <t>Carla Alfredo Albino</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3918786000006032043</t>
+          <t>3918786000006032039</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Marlene João Alfredo</t>
+          <t>Carla Alfredo Albino</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -464,22 +464,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3918786000010015006</t>
+          <t>3918786000010015010</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -489,12 +489,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>3918786000010236128</t>
+          <t>3918786000010257890</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -516,22 +516,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adino João</t>
+          <t>Marlene João Alfredo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3918786000006059003</t>
+          <t>3918786000006032043</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Adino João</t>
+          <t>Marlene João Alfredo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -541,17 +541,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NACARROANE</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3918786000010015016</t>
+          <t>3918786000010015006</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NACARROANE</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -566,12 +566,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3918786000010236126</t>
+          <t>3918786000010236128</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -588,27 +588,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Juleca Felisberto</t>
+          <t>Adino João</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3918786000006032011</t>
+          <t>3918786000006059003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Juleca Felisberto</t>
+          <t>Adino João</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -618,17 +618,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>NACARROANE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3918786000010015032</t>
+          <t>3918786000010015016</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>NACARROANE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -643,17 +643,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3918786000010230642</t>
+          <t>3918786000010236126</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -695,17 +695,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3918786000010015030</t>
+          <t>3918786000010015032</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3918786000010230640</t>
+          <t>3918786000010230642</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -742,27 +742,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Agostinho Júlio Adelino</t>
+          <t>Juleca Felisberto</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3918786000006032027</t>
+          <t>3918786000006032011</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Agostinho Júlio Adelino</t>
+          <t>Juleca Felisberto</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3918786000010015014</t>
+          <t>3918786000010015030</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -797,17 +797,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3918786000010230046</t>
+          <t>3918786000010230640</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>07-May-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3918786000010230044</t>
+          <t>3918786000010230046</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -896,7 +896,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3918786000010230042</t>
+          <t>3918786000010230044</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -973,7 +973,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3918786000010230040</t>
+          <t>3918786000010230042</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1050,7 +1050,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3918786000010230038</t>
+          <t>3918786000010230040</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1127,7 +1127,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3918786000010230036</t>
+          <t>3918786000010230038</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1204,7 +1204,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3918786000010230034</t>
+          <t>3918786000010230036</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>19-Mar-2026</t>
+          <t>26-Mar-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3918786000010230032</t>
+          <t>3918786000010230034</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12-Mar-2026</t>
+          <t>19-Mar-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>3918786000010230030</t>
+          <t>3918786000010230032</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1435,7 +1435,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>12-Mar-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1490,12 +1490,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3918786000010230028</t>
+          <t>3918786000010230030</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1505,14 +1505,14 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>29-Apr-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1557,22 +1557,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3918786000010230026</t>
+          <t>3918786000010230028</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1582,14 +1582,14 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>29-Apr-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1634,22 +1634,22 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3918786000010230024</t>
+          <t>3918786000010230026</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1691,42 +1691,42 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3918786000010015014</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>NAMUALI</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>3918786000010015014</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>NAMUALI</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Sessão_6</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3918786000010230022</t>
+          <t>3918786000010230024</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1736,14 +1736,14 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1788,22 +1788,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3918786000010230020</t>
+          <t>3918786000010230022</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1813,14 +1813,14 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3918786000010230018</t>
+          <t>3918786000010230020</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1890,14 +1890,14 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1942,22 +1942,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>3918786000010230016</t>
+          <t>3918786000010230018</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2019,22 +2019,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>3918786000010230014</t>
+          <t>3918786000010230016</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2051,7 +2051,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>18-Mar-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2076,42 +2076,42 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3918786000010015014</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>NAMUALI</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>3918786000010015014</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>NAMUALI</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Sessão_1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>3918786000010230012</t>
+          <t>3918786000010230014</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2173,22 +2173,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3918786000010230010</t>
+          <t>3918786000010230012</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2198,14 +2198,14 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>3918786000010230008</t>
+          <t>3918786000010230010</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2275,14 +2275,14 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>3918786000010230006</t>
+          <t>3918786000010230008</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2359,104 +2359,104 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Marlene João Alfredo</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3918786000006032043</t>
+          <t>3918786000006032027</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Marlene João Alfredo</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3918786000010015014</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>NAMUALI</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3918786000010230006</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Ribaue</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>NAMALE</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>3918786000010015006</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>NAMALE</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Sessão_9</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>3918786000010227042</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Ribaue</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Albertina Cualeia</t>
+          <t>Marlene João Alfredo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3918786000006032031</t>
+          <t>3918786000006032043</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Albertina Cualeia</t>
+          <t>Marlene João Alfredo</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2466,22 +2466,22 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MANICA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3918786000010015012</t>
+          <t>3918786000010015006</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MANICA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>3918786000010225205</t>
+          <t>3918786000010227042</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2518,22 +2518,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Marlene João Alfredo</t>
+          <t>Albertina Cualeia</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3918786000006032043</t>
+          <t>3918786000006032031</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Marlene João Alfredo</t>
+          <t>Albertina Cualeia</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2543,17 +2543,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>MANICA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3918786000010015004</t>
+          <t>3918786000010015012</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>MANICA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3918786000010225203</t>
+          <t>3918786000010225205</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2590,7 +2590,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3918786000010225201</t>
+          <t>3918786000010225203</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3918786000010225199</t>
+          <t>3918786000010225201</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2744,27 +2744,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Albertina Cualeia</t>
+          <t>Marlene João Alfredo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3918786000006032031</t>
+          <t>3918786000006032043</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Albertina Cualeia</t>
+          <t>Marlene João Alfredo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2774,22 +2774,22 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MANICA</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3918786000010015012</t>
+          <t>3918786000010015004</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MANICA</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>3918786000010225052</t>
+          <t>3918786000010225199</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2821,7 +2821,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3918786000010225050</t>
+          <t>3918786000010225052</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>3918786000010225048</t>
+          <t>3918786000010225050</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2975,7 +2975,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>29-Apr-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3918786000010225046</t>
+          <t>3918786000010225048</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3052,7 +3052,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>29-Apr-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>3918786000010225044</t>
+          <t>3918786000010225046</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>3918786000010225042</t>
+          <t>3918786000010225044</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3206,7 +3206,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>3918786000010225040</t>
+          <t>3918786000010225042</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3283,7 +3283,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3338,12 +3338,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>3918786000010225038</t>
+          <t>3918786000010225040</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>3918786000010225036</t>
+          <t>3918786000010225038</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3437,7 +3437,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>3918786000010225034</t>
+          <t>3918786000010225036</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3514,7 +3514,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>3918786000010225032</t>
+          <t>3918786000010225034</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>3918786000010225030</t>
+          <t>3918786000010225032</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3668,7 +3668,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>3918786000010225028</t>
+          <t>3918786000010225030</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3745,7 +3745,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>3918786000010225026</t>
+          <t>3918786000010225028</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>33</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>3918786000010225024</t>
+          <t>3918786000010225026</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3899,7 +3899,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>3918786000010225022</t>
+          <t>3918786000010225024</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3976,7 +3976,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>3918786000010225020</t>
+          <t>3918786000010225022</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>3918786000010225018</t>
+          <t>3918786000010225020</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4130,7 +4130,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>3918786000010225016</t>
+          <t>3918786000010225018</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4207,7 +4207,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>3918786000010225014</t>
+          <t>3918786000010225016</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4284,7 +4284,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>3918786000010225012</t>
+          <t>3918786000010225014</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>26</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>3918786000010225010</t>
+          <t>3918786000010225012</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4438,7 +4438,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>18-Mar-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>3918786000010225008</t>
+          <t>3918786000010225010</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4515,7 +4515,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>12-Mar-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>3918786000010225006</t>
+          <t>3918786000010225008</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4592,7 +4592,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>12-Mar-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>26</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>3918786000010225004</t>
+          <t>3918786000010225006</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>33</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>3918786000010225002</t>
+          <t>3918786000010225004</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4746,22 +4746,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Marlene João Alfredo</t>
+          <t>Albertina Cualeia</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3918786000006032043</t>
+          <t>3918786000006032031</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Marlene João Alfredo</t>
+          <t>Albertina Cualeia</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4776,22 +4776,22 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>MANICA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3918786000010015004</t>
+          <t>3918786000010015012</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>MANICA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>3918786000010224040</t>
+          <t>3918786000010225002</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4823,7 +4823,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>3918786000010219712</t>
+          <t>3918786000010224040</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4900,7 +4900,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>07-May-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>3918786000010219710</t>
+          <t>3918786000010219712</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4977,7 +4977,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>3918786000010219708</t>
+          <t>3918786000010219710</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5054,22 +5054,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Carla Alfredo Albino</t>
+          <t>Marlene João Alfredo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>3918786000006032039</t>
+          <t>3918786000006032043</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Carla Alfredo Albino</t>
+          <t>Marlene João Alfredo</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5084,22 +5084,22 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>MANICA</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>3918786000010015008</t>
+          <t>3918786000010015004</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>MANICA</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>3918786000010219706</t>
+          <t>3918786000010219708</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5131,7 +5131,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5186,12 +5186,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>3918786000010219704</t>
+          <t>3918786000010219706</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5208,7 +5208,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>3918786000010219702</t>
+          <t>3918786000010219704</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5285,7 +5285,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>3918786000010219700</t>
+          <t>3918786000010219702</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5362,7 +5362,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5417,12 +5417,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>3918786000010219698</t>
+          <t>3918786000010219700</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5439,7 +5439,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>3918786000010219696</t>
+          <t>3918786000010219698</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5516,7 +5516,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>27-Mar-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5571,12 +5571,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>3918786000010219694</t>
+          <t>3918786000010219696</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5593,7 +5593,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20-Mar-2026</t>
+          <t>27-Mar-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>3918786000010219692</t>
+          <t>3918786000010219694</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5670,7 +5670,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>12-Mar-2026</t>
+          <t>20-Mar-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>3918786000010219690</t>
+          <t>3918786000010219692</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5747,7 +5747,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>12-Mar-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5777,22 +5777,22 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
+          <t>MANICA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>3918786000010015010</t>
+          <t>3918786000010015008</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
+          <t>MANICA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>3918786000010219688</t>
+          <t>3918786000010219690</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5824,7 +5824,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>29-Apr-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>3918786000010219686</t>
+          <t>3918786000010219688</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5901,7 +5901,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>29-Apr-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>3918786000010219684</t>
+          <t>3918786000010219686</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5978,7 +5978,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>26</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>3918786000010219682</t>
+          <t>3918786000010219684</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -6055,7 +6055,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>3918786000010219680</t>
+          <t>3918786000010219682</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -6132,7 +6132,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>3918786000010219678</t>
+          <t>3918786000010219680</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -6209,7 +6209,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>3918786000010219676</t>
+          <t>3918786000010219678</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -6286,7 +6286,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>3918786000010219674</t>
+          <t>3918786000010219676</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6363,7 +6363,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>18-Mar-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>3918786000010219672</t>
+          <t>3918786000010219674</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6440,7 +6440,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6485,22 +6485,22 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>3918786000010219670</t>
+          <t>3918786000010219672</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6517,7 +6517,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6562,22 +6562,22 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>3918786000010219668</t>
+          <t>3918786000010219670</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6594,7 +6594,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>3918786000010219666</t>
+          <t>3918786000010219668</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6671,7 +6671,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>3918786000010219664</t>
+          <t>3918786000010219666</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6748,7 +6748,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>3918786000010219662</t>
+          <t>3918786000010219664</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6825,7 +6825,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6880,12 +6880,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>3918786000010219660</t>
+          <t>3918786000010219662</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6902,7 +6902,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>3918786000010219658</t>
+          <t>3918786000010219660</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6979,7 +6979,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>3918786000010219656</t>
+          <t>3918786000010219658</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -7056,7 +7056,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -7111,12 +7111,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>3918786000010219654</t>
+          <t>3918786000010219656</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -7133,27 +7133,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10-May-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Esperança Armando</t>
+          <t>Carla Alfredo Albino</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>3918786000006032007</t>
+          <t>3918786000006032039</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Esperança Armando</t>
+          <t>Carla Alfredo Albino</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7163,22 +7163,22 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>3918786000010015028</t>
+          <t>3918786000010015010</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -7188,17 +7188,17 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>3918786000010219152</t>
+          <t>3918786000010219654</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7240,22 +7240,22 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>3918786000010015026</t>
+          <t>3918786000010015028</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>50</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>3918786000010219150</t>
+          <t>3918786000010219152</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7317,22 +7317,22 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>3918786000010015028</t>
+          <t>3918786000010015026</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>3918786000010219148</t>
+          <t>3918786000010219150</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>3918786000010219146</t>
+          <t>3918786000010219148</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7471,22 +7471,22 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>3918786000010015026</t>
+          <t>3918786000010015028</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>49</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>3918786000010219144</t>
+          <t>3918786000010219146</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>3918786000010219142</t>
+          <t>3918786000010219144</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7595,22 +7595,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>10-May-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Adino João</t>
+          <t>Esperança Armando</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>3918786000006059003</t>
+          <t>3918786000006032007</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Adino João</t>
+          <t>Esperança Armando</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7625,22 +7625,22 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>NACARROANE</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>3918786000010015016</t>
+          <t>3918786000010015026</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>NACARROANE</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7650,17 +7650,17 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>39</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>3918786000010215076</t>
+          <t>3918786000010219142</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -7672,7 +7672,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>07-May-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>3918786000010215074</t>
+          <t>3918786000010215076</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7749,7 +7749,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>3918786000010215072</t>
+          <t>3918786000010215074</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7826,7 +7826,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>3918786000010215070</t>
+          <t>3918786000010215072</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7903,7 +7903,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>3918786000010215068</t>
+          <t>3918786000010215070</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>3918786000010215066</t>
+          <t>3918786000010215068</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -8057,7 +8057,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>3918786000010215064</t>
+          <t>3918786000010215066</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -8134,7 +8134,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>19-Mar-2026</t>
+          <t>26-Mar-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>3918786000010215062</t>
+          <t>3918786000010215064</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -8211,7 +8211,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>12-Mar-2026</t>
+          <t>19-Mar-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>3918786000010215060</t>
+          <t>3918786000010215062</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -8288,7 +8288,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>12-Mar-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -8343,12 +8343,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>3918786000010215058</t>
+          <t>3918786000010215060</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -8365,7 +8365,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>29-Apr-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>3918786000010215056</t>
+          <t>3918786000010215058</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -8442,7 +8442,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>29-Apr-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>3918786000010215054</t>
+          <t>3918786000010215056</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -8519,7 +8519,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>3918786000010215052</t>
+          <t>3918786000010215054</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8596,7 +8596,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>3918786000010215050</t>
+          <t>3918786000010215052</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8673,7 +8673,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>3918786000010215048</t>
+          <t>3918786000010215050</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8750,7 +8750,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>3918786000010215046</t>
+          <t>3918786000010215048</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8827,7 +8827,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>3918786000010215044</t>
+          <t>3918786000010215046</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8904,7 +8904,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>18-Mar-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>3918786000010215042</t>
+          <t>3918786000010215044</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8981,7 +8981,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>3918786000010215040</t>
+          <t>3918786000010215042</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -9058,7 +9058,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>07-May-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -9113,12 +9113,12 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>3918786000010215038</t>
+          <t>3918786000010215040</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -9135,7 +9135,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -9190,12 +9190,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>3918786000010215036</t>
+          <t>3918786000010215038</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -9212,7 +9212,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>3918786000010215034</t>
+          <t>3918786000010215036</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -9289,7 +9289,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>3918786000010215032</t>
+          <t>3918786000010215034</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -9366,7 +9366,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>3918786000010215030</t>
+          <t>3918786000010215032</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -9443,7 +9443,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>3918786000010215028</t>
+          <t>3918786000010215030</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -9520,7 +9520,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>3918786000010215026</t>
+          <t>3918786000010215028</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9597,7 +9597,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>3918786000010215024</t>
+          <t>3918786000010215026</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9674,27 +9674,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>12-Mar-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Domingas Albino</t>
+          <t>Adino João</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>3918786000006032003</t>
+          <t>3918786000006059003</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Domingas Albino</t>
+          <t>Adino João</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -9704,17 +9704,17 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NACARROANE</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>3918786000010015022</t>
+          <t>3918786000010015016</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NACARROANE</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -9724,22 +9724,22 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>3918786000010210032</t>
+          <t>3918786000010215024</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -9751,7 +9751,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>12-Mar-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -9781,17 +9781,17 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>MUTOCONE</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>3918786000010015024</t>
+          <t>3918786000010015022</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>MUTOCONE</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -9801,17 +9801,17 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>3918786000010210030</t>
+          <t>3918786000010210032</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9828,7 +9828,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>19-Mar-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -9858,37 +9858,37 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MUTOCONE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>3918786000010015022</t>
+          <t>3918786000010015024</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MUTOCONE</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>3918786000010210028</t>
+          <t>3918786000010210030</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9905,7 +9905,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>19-Mar-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -9935,17 +9935,17 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>MUTOCONE</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>3918786000010015024</t>
+          <t>3918786000010015022</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>MUTOCONE</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -9955,17 +9955,17 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>3918786000010210026</t>
+          <t>3918786000010210028</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9982,7 +9982,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -10012,37 +10012,37 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MUTOCONE</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>3918786000010015022</t>
+          <t>3918786000010015024</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MUTOCONE</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>3918786000010210024</t>
+          <t>3918786000010210026</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -10059,7 +10059,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>26-Mar-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -10089,17 +10089,17 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>MUTOCONE</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>3918786000010015024</t>
+          <t>3918786000010015022</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>MUTOCONE</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -10114,12 +10114,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>3918786000010210022</t>
+          <t>3918786000010210024</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -10136,7 +10136,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -10166,22 +10166,22 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MUTOCONE</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>3918786000010015022</t>
+          <t>3918786000010015024</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MUTOCONE</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>39</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>3918786000010210020</t>
+          <t>3918786000010210022</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -10213,7 +10213,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -10243,17 +10243,17 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>MUTOCONE</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>3918786000010015024</t>
+          <t>3918786000010015022</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>MUTOCONE</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -10268,12 +10268,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>3918786000010210018</t>
+          <t>3918786000010210020</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -10290,7 +10290,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10320,22 +10320,22 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MUTOCONE</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>3918786000010015022</t>
+          <t>3918786000010015024</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MUTOCONE</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -10345,12 +10345,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>3918786000010210016</t>
+          <t>3918786000010210018</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -10367,7 +10367,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>12-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -10397,17 +10397,17 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>MUTOCONE</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>3918786000010015024</t>
+          <t>3918786000010015022</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>MUTOCONE</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -10422,12 +10422,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>3918786000010210014</t>
+          <t>3918786000010210016</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -10444,7 +10444,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>12-Apr-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -10474,22 +10474,22 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MUTOCONE</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>3918786000010015022</t>
+          <t>3918786000010015024</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MUTOCONE</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -10499,12 +10499,12 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>33</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>3918786000010210012</t>
+          <t>3918786000010210014</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -10521,7 +10521,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10551,17 +10551,17 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>MUTOCONE</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>3918786000010015024</t>
+          <t>3918786000010015022</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>MUTOCONE</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>3918786000010210010</t>
+          <t>3918786000010210012</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10598,7 +10598,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10628,22 +10628,22 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MUTOCONE</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>3918786000010015022</t>
+          <t>3918786000010015024</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MUTOCONE</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -10653,12 +10653,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>39</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>3918786000010210008</t>
+          <t>3918786000010210010</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10675,7 +10675,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -10705,17 +10705,17 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>MUTOCONE</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>3918786000010015024</t>
+          <t>3918786000010015022</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>MUTOCONE</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -10730,12 +10730,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>3918786000010210006</t>
+          <t>3918786000010210008</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10752,7 +10752,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -10807,12 +10807,12 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>3918786000010210004</t>
+          <t>3918786000010210006</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10829,7 +10829,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -10859,17 +10859,17 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MUTOCONE</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>3918786000010015022</t>
+          <t>3918786000010015024</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>MUTOCONE</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -10884,12 +10884,12 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>39</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>3918786000010210002</t>
+          <t>3918786000010210004</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10906,27 +10906,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>07-May-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Carla Alfredo Albino</t>
+          <t>Domingas Albino</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>3918786000006032039</t>
+          <t>3918786000006032003</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Carla Alfredo Albino</t>
+          <t>Domingas Albino</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -10936,22 +10936,22 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>3918786000010015010</t>
+          <t>3918786000010015022</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -10961,17 +10961,17 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>3918786000010204280</t>
+          <t>3918786000010210002</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -10983,7 +10983,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -11013,17 +11013,17 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>MANICA</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>3918786000010015008</t>
+          <t>3918786000010015010</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>MANICA</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>50</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>3918786000010204010</t>
+          <t>3918786000010204280</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -11060,7 +11060,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>3918786000010204008</t>
+          <t>3918786000010204010</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -11137,22 +11137,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Esperança Armando</t>
+          <t>Carla Alfredo Albino</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>3918786000006032007</t>
+          <t>3918786000006032039</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Esperança Armando</t>
+          <t>Carla Alfredo Albino</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -11167,22 +11167,22 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>MANICA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>3918786000010015026</t>
+          <t>3918786000010015008</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>MANICA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -11192,17 +11192,17 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>28</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>3918786000010201292</t>
+          <t>3918786000010204008</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -11214,22 +11214,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Juleca Felisberto</t>
+          <t>Esperança Armando</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>3918786000006032011</t>
+          <t>3918786000006032007</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Juleca Felisberto</t>
+          <t>Esperança Armando</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -11244,22 +11244,22 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>3918786000010015032</t>
+          <t>3918786000010015026</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>42</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>3918786000010183222</t>
+          <t>3918786000010201292</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -11291,7 +11291,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>14-May-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11321,17 +11321,17 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>3918786000010015030</t>
+          <t>3918786000010015032</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>3918786000010183220</t>
+          <t>3918786000010183222</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>3918786000010183218</t>
+          <t>3918786000010183220</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -11475,17 +11475,17 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>3918786000010015032</t>
+          <t>3918786000010015030</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>28</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>3918786000010183216</t>
+          <t>3918786000010183218</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -11522,7 +11522,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>07-May-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11552,22 +11552,22 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>3918786000010015030</t>
+          <t>3918786000010015032</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -11577,12 +11577,12 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>3918786000010183214</t>
+          <t>3918786000010183216</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -11599,7 +11599,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>14-May-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>3918786000010183212</t>
+          <t>3918786000010183214</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11706,17 +11706,17 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>3918786000010015032</t>
+          <t>3918786000010015030</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -11731,12 +11731,12 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>3918786000010183210</t>
+          <t>3918786000010183212</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11798,7 +11798,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>54</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>3918786000010183208</t>
+          <t>3918786000010183210</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11860,17 +11860,17 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>3918786000010015030</t>
+          <t>3918786000010015032</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>46</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>3918786000010183206</t>
+          <t>3918786000010183208</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11937,22 +11937,22 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>3918786000010015032</t>
+          <t>3918786000010015030</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -11962,12 +11962,12 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>3918786000010183204</t>
+          <t>3918786000010183206</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -12039,12 +12039,12 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>3918786000010183202</t>
+          <t>3918786000010183204</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -12116,12 +12116,12 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>3918786000010183200</t>
+          <t>3918786000010183202</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -12168,22 +12168,22 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>3918786000010015030</t>
+          <t>3918786000010015032</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>NICANE</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>37</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>3918786000010183198</t>
+          <t>3918786000010183200</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -12270,12 +12270,12 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>3918786000010183196</t>
+          <t>3918786000010183198</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>3918786000010183194</t>
+          <t>3918786000010183196</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -12369,22 +12369,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>07-May-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Marlene João Alfredo</t>
+          <t>Juleca Felisberto</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>3918786000006032043</t>
+          <t>3918786000006032011</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Marlene João Alfredo</t>
+          <t>Juleca Felisberto</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -12399,22 +12399,22 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>3918786000010015006</t>
+          <t>3918786000010015030</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>NICANE</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -12424,17 +12424,17 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>36</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>3918786000010178172</t>
+          <t>3918786000010183194</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>Ribaue</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -12446,7 +12446,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>3918786000010178170</t>
+          <t>3918786000010178172</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -12523,7 +12523,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>03-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -12578,12 +12578,12 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>3918786000010178168</t>
+          <t>3918786000010178170</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -12600,7 +12600,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>03-Apr-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -12630,17 +12630,17 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>3918786000010015004</t>
+          <t>3918786000010015006</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>3918786000010178166</t>
+          <t>3918786000010178168</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12677,7 +12677,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12697,7 +12697,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -12707,17 +12707,17 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>3918786000010015006</t>
+          <t>3918786000010015004</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -12737,7 +12737,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>3918786000010178164</t>
+          <t>3918786000010178166</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12754,7 +12754,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -12784,17 +12784,17 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>3918786000010015004</t>
+          <t>3918786000010015006</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>3918786000010178162</t>
+          <t>3918786000010178164</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12831,7 +12831,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>27-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12861,22 +12861,22 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>3918786000010015006</t>
+          <t>3918786000010015004</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -12886,12 +12886,12 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>3918786000010178160</t>
+          <t>3918786000010178162</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12908,7 +12908,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>27-Mar-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -12938,17 +12938,17 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>3918786000010015004</t>
+          <t>3918786000010015006</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>3918786000010178158</t>
+          <t>3918786000010178160</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12985,7 +12985,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>26-Mar-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13005,27 +13005,27 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>3918786000010015006</t>
+          <t>3918786000010015004</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -13035,17 +13035,17 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>3918786000010178156</t>
+          <t>3918786000010178158</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -13062,7 +13062,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13082,27 +13082,27 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>3918786000010015004</t>
+          <t>3918786000010015006</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -13112,17 +13112,17 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>3918786000010178154</t>
+          <t>3918786000010178156</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -13139,7 +13139,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>20-Mar-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -13169,22 +13169,22 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>3918786000010015006</t>
+          <t>3918786000010015004</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -13194,12 +13194,12 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>3918786000010178110</t>
+          <t>3918786000010178154</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -13216,7 +13216,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>19-Mar-2026</t>
+          <t>20-Mar-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -13246,17 +13246,17 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>3918786000010015004</t>
+          <t>3918786000010015006</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -13271,12 +13271,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>3918786000010178108</t>
+          <t>3918786000010178110</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -13293,7 +13293,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>19-Mar-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13313,27 +13313,27 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>3918786000010015006</t>
+          <t>3918786000010015004</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -13348,12 +13348,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>3918786000010178106</t>
+          <t>3918786000010178108</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -13370,7 +13370,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>18-Mar-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13395,22 +13395,22 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>3918786000010015004</t>
+          <t>3918786000010015006</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -13425,12 +13425,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>3918786000010178104</t>
+          <t>3918786000010178106</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -13447,7 +13447,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>13-Mar-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -13477,22 +13477,22 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>3918786000010015006</t>
+          <t>3918786000010015004</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -13502,12 +13502,12 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>3918786000010178102</t>
+          <t>3918786000010178104</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -13524,7 +13524,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>12-Mar-2026</t>
+          <t>13-Mar-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -13554,17 +13554,17 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>3918786000010015004</t>
+          <t>3918786000010015006</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>NAMARIESSA</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -13579,12 +13579,12 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>3918786000010178100</t>
+          <t>3918786000010178102</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -13601,7 +13601,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>12-Mar-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -13631,17 +13631,17 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>3918786000010015006</t>
+          <t>3918786000010015004</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>NAMALE</t>
+          <t>NAMARIESSA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -13651,17 +13651,17 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>3918786000010178058</t>
+          <t>3918786000010178100</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13678,7 +13678,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>29-Apr-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -13723,22 +13723,22 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>3918786000010173394</t>
+          <t>3918786000010178058</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13755,7 +13755,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>29-Apr-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -13810,12 +13810,12 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>3918786000010173392</t>
+          <t>3918786000010173394</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13832,27 +13832,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Sérgio Rafael</t>
+          <t>Marlene João Alfredo</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>3918786000006987003</t>
+          <t>3918786000006032043</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Sérgio Rafael</t>
+          <t>Marlene João Alfredo</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -13862,22 +13862,22 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>3918786000010015020</t>
+          <t>3918786000010015006</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>NAMALE</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -13887,12 +13887,12 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>42</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>3918786000010173390</t>
+          <t>3918786000010173392</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13909,7 +13909,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13929,12 +13929,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -13964,12 +13964,12 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>3918786000010173388</t>
+          <t>3918786000010173390</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13986,7 +13986,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14006,12 +14006,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>3918786000010173386</t>
+          <t>3918786000010173388</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -14063,7 +14063,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -14118,12 +14118,12 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>3918786000010173384</t>
+          <t>3918786000010173386</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -14140,7 +14140,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>3918786000010173382</t>
+          <t>3918786000010173384</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -14217,7 +14217,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -14272,12 +14272,12 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>3918786000010173380</t>
+          <t>3918786000010173382</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -14294,7 +14294,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14314,7 +14314,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -14339,22 +14339,22 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>3918786000010173378</t>
+          <t>3918786000010173380</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -14371,7 +14371,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -14416,22 +14416,22 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>3918786000010173376</t>
+          <t>3918786000010173378</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -14448,7 +14448,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14493,7 +14493,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -14508,7 +14508,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>3918786000010173374</t>
+          <t>3918786000010173376</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -14525,7 +14525,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14545,7 +14545,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -14555,22 +14555,22 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>3918786000010015018</t>
+          <t>3918786000010015020</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>MICUE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -14580,12 +14580,12 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>3918786000010173372</t>
+          <t>3918786000010173374</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -14602,7 +14602,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>29-Apr-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -14647,22 +14647,22 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>3918786000010173370</t>
+          <t>3918786000010173372</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -14679,7 +14679,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>29-Apr-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14699,12 +14699,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14724,22 +14724,22 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>3918786000010173368</t>
+          <t>3918786000010173370</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14756,7 +14756,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14776,47 +14776,47 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>3918786000010015018</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>MICUE</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>3918786000010015018</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>MICUE</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>Sessão_6</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>3918786000010173366</t>
+          <t>3918786000010173368</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14833,7 +14833,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14853,7 +14853,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -14878,22 +14878,22 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>3918786000010173364</t>
+          <t>3918786000010173366</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14910,7 +14910,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14930,47 +14930,47 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>3918786000010015018</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>MICUE</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>MICUE</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>3918786000010015018</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>MICUE</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>Sessão_4</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>3918786000010173362</t>
+          <t>3918786000010173364</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14987,7 +14987,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -15032,22 +15032,22 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>3918786000010173360</t>
+          <t>3918786000010173362</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -15064,7 +15064,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15084,7 +15084,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -15109,7 +15109,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -15119,12 +15119,12 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>3918786000010173358</t>
+          <t>3918786000010173360</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -15141,7 +15141,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>18-Mar-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>3918786000010173356</t>
+          <t>3918786000010173358</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -15218,27 +15218,27 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>19-Mar-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Carla Alfredo Albino</t>
+          <t>Sérgio Rafael</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>3918786000006032039</t>
+          <t>3918786000006987003</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Carla Alfredo Albino</t>
+          <t>Sérgio Rafael</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -15248,22 +15248,22 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
+          <t>MICUE</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>3918786000010015010</t>
+          <t>3918786000010015018</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>CURRAPE</t>
+          <t>MICUE</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>42</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>3918786000010172009</t>
+          <t>3918786000010173356</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -15295,27 +15295,27 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>19-Mar-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Agostinho Júlio Adelino</t>
+          <t>Carla Alfredo Albino</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>3918786000006032027</t>
+          <t>3918786000006032039</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Agostinho Júlio Adelino</t>
+          <t>Carla Alfredo Albino</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -15325,22 +15325,22 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>3918786000010015014</t>
+          <t>3918786000010015010</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>NAMUALI</t>
+          <t>CURRAPE</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -15350,12 +15350,12 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>3918786000010125016</t>
+          <t>3918786000010172009</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -15372,7 +15372,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -15417,7 +15417,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -15427,12 +15427,12 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>3918786000010125014</t>
+          <t>3918786000010125016</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -15442,14 +15442,14 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -15504,12 +15504,12 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>3918786000010125012</t>
+          <t>3918786000010125014</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -15519,14 +15519,14 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -15581,12 +15581,12 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>3918786000010125010</t>
+          <t>3918786000010125012</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -15603,7 +15603,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -15663,7 +15663,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>3918786000010125008</t>
+          <t>3918786000010125010</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -15680,7 +15680,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>3918786000010125006</t>
+          <t>3918786000010125008</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15757,7 +15757,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -15802,7 +15802,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -15812,12 +15812,12 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>3918786000010125004</t>
+          <t>3918786000010125006</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15834,7 +15834,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15854,7 +15854,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -15894,7 +15894,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>3918786000010125002</t>
+          <t>3918786000010125004</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15911,27 +15911,27 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>18-Apr-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>3918786000006032015</t>
+          <t>3918786000006032027</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Mainote Momade</t>
+          <t>Agostinho Júlio Adelino</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -15941,22 +15941,22 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>3918786000010015036</t>
+          <t>3918786000010015014</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>MURROMONE</t>
+          <t>NAMUALI</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -15966,17 +15966,17 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>3918786000010071142</t>
+          <t>3918786000010125002</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Ribaue</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -15988,7 +15988,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>25-Apr-2026</t>
+          <t>18-Apr-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -16043,12 +16043,12 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>3918786000010071140</t>
+          <t>3918786000010071142</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -16065,7 +16065,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>18-Apr-2026</t>
+          <t>25-Apr-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16085,7 +16085,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -16110,7 +16110,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -16120,12 +16120,12 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>3918786000010071138</t>
+          <t>3918786000010071140</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -16187,22 +16187,22 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>3918786000010071136</t>
+          <t>3918786000010071138</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -16264,22 +16264,22 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>3918786000010071134</t>
+          <t>3918786000010071136</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -16316,12 +16316,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>3918786000010071132</t>
+          <t>3918786000010071134</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -16393,47 +16393,47 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>JARDIM</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>3918786000010015034</t>
+          <t>3918786000010015036</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>JARDIM</t>
+          <t>MURROMONE</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>3918786000010071130</t>
+          <t>3918786000010071132</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -16495,7 +16495,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -16505,12 +16505,12 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>3918786000010071128</t>
+          <t>3918786000010071130</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -16547,7 +16547,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -16572,7 +16572,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -16582,12 +16582,12 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>3918786000010071126</t>
+          <t>3918786000010071128</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -16624,7 +16624,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -16634,37 +16634,37 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>JARDIM</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>3918786000010015038</t>
+          <t>3918786000010015034</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>OFENSIVA</t>
+          <t>JARDIM</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>3918786000010071124</t>
+          <t>3918786000010071126</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -16701,47 +16701,47 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>OFENSIVA</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>3918786000010015038</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>OFENSIVA</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>OFENSIVA</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>3918786000010015038</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>OFENSIVA</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>Sessão_2</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>3918786000010071122</t>
+          <t>3918786000010071124</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16778,7 +16778,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -16803,22 +16803,22 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>3918786000010071120</t>
+          <t>3918786000010071122</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16865,37 +16865,37 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>JARDIM</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>3918786000010015034</t>
+          <t>3918786000010015038</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>JARDIM</t>
+          <t>OFENSIVA</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>3918786000010071118</t>
+          <t>3918786000010071120</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16932,47 +16932,47 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>3918786000010015034</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>JARDIM</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>3918786000010015034</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>JARDIM</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>Sessão_2</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>3918786000010071116</t>
+          <t>3918786000010071118</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -17034,22 +17034,22 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>3918786000010071114</t>
+          <t>3918786000010071116</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -17066,75 +17066,152 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>3918786000006032015</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Mainote Momade</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>3918786000010015034</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>JARDIM</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>3918786000010071114</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
           <t>10-Mar-2026</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>Marlene João Alfredo</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
+      <c r="C219" t="inlineStr">
         <is>
           <t>3918786000006032043</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>Marlene João Alfredo</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
+      <c r="E219" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
         <is>
           <t>NAMARIESSA</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
+      <c r="H219" t="inlineStr">
         <is>
           <t>3918786000010015004</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
+      <c r="I219" t="inlineStr">
         <is>
           <t>NAMARIESSA</t>
         </is>
       </c>
-      <c r="J218" t="inlineStr">
+      <c r="J219" t="inlineStr">
         <is>
           <t>Sessão_1</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr">
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr">
+      <c r="M219" t="inlineStr">
         <is>
           <t>3918786000010015294</t>
         </is>
       </c>
-      <c r="N218" t="inlineStr">
+      <c r="N219" t="inlineStr">
         <is>
           <t>Ribaue</t>
         </is>
       </c>
-      <c r="O218" t="inlineStr">
+      <c r="O219" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -17401,13 +17478,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9995DF3C-924C-46F5-BC3E-CAE32DE0E3A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB9B3FD8-B3E8-4A3B-B591-3D9F368A4754}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EDA3F80-EF27-48B7-A482-B455D7906537}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74F4F083-940A-4F53-A051-59DCB5C7FA72}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38C66B80-772C-472F-A618-CD2A183EF0AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10B4C99C-D798-44C8-A9DE-24E467C86608}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -17220,271 +17220,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
-    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB9B3FD8-B3E8-4A3B-B591-3D9F368A4754}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74F4F083-940A-4F53-A051-59DCB5C7FA72}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10B4C99C-D798-44C8-A9DE-24E467C86608}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -17220,4 +17220,271 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
+    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07721C6D-DFBB-4CDE-AEDA-2F599449509A}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1976BDA2-8F2B-4A0F-9F0F-C041022FE531}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C97B8E7-418B-4855-8E96-9DD6B26A3290}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -17374,4 +17374,271 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
+    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72780812-E248-4BEA-9F1D-CA243D52B612}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{283B6916-1AC7-4F4E-B58D-735484E14B58}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{643E6A08-5E0D-4EB6-B424-3AF000E004F4}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -20404,13 +20404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFCE4BDB-04F7-42C4-BDD1-BF61184B38C6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27F33E82-8B79-429A-B44C-6895F068EC14}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2164D4A4-D474-461E-9098-E18FDF71F4D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A99058B7-21ED-4B08-8028-9FD8543D4AC1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9EF165B-9892-4FF9-9E43-527584CD54A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E117CA7-30B9-4164-9654-80F1683D2220}"/>
 </file>